--- a/merchant_forms/001_custom_t_shirt_order_form_template--merchant_forms.xlsx
+++ b/merchant_forms/001_custom_t_shirt_order_form_template--merchant_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -822,12 +822,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C19"/>
+  <dimension ref="A1:C18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="25" customWidth="1" min="1" max="1"/>
-    <col width="48" customWidth="1" min="2" max="2"/>
-    <col width="48" customWidth="1" min="3" max="3"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -855,12 +855,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'label':_'payment_method',_'value':_'paypal'}</t>
+          <t>payment_method</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'label': 'Payment Method', 'value': 'PayPal'}</t>
+          <t>Payment Method</t>
         </is>
       </c>
     </row>
@@ -872,29 +872,29 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'label':_'payment_method',_'value':_'stripe'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'label': 'Payment Method', 'value': 'Stripe'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>payment_method_choices</t>
+          <t>tshirt_design_choices</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'label':_'payment_method',_'value':_'other'}</t>
+          <t>red_t-shirt</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'label': 'Payment Method', 'value': 'Other'}</t>
+          <t>Red T-Shirt</t>
         </is>
       </c>
     </row>
@@ -906,12 +906,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'label':_'red_t-shirt'}</t>
+          <t>blue_t-shirt</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'label': 'Red T-Shirt'}</t>
+          <t>Blue T-Shirt</t>
         </is>
       </c>
     </row>
@@ -923,29 +923,29 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'label':_'blue_t-shirt'}</t>
+          <t>green_t-shirt</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'label': 'Blue T-Shirt'}</t>
+          <t>Green T-Shirt</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>tshirt_design_choices</t>
+          <t>tshirt_size_choices</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'label':_'green_t-shirt'}</t>
+          <t>small</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'label': 'Green T-Shirt'}</t>
+          <t>Small</t>
         </is>
       </c>
     </row>
@@ -957,12 +957,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'label':_'small'}</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'label': 'Small'}</t>
+          <t>Medium</t>
         </is>
       </c>
     </row>
@@ -974,29 +974,29 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'label':_'medium'}</t>
+          <t>large</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'label': 'Medium'}</t>
+          <t>Large</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>tshirt_size_choices</t>
+          <t>tshirt_color_choices</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'label':_'large'}</t>
+          <t>red</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'label': 'Large'}</t>
+          <t>Red</t>
         </is>
       </c>
     </row>
@@ -1008,12 +1008,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'label':_'red'}</t>
+          <t>blue</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'label': 'Red'}</t>
+          <t>Blue</t>
         </is>
       </c>
     </row>
@@ -1025,29 +1025,29 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'label':_'blue'}</t>
+          <t>white</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'label': 'Blue'}</t>
+          <t>White</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>tshirt_color_choices</t>
+          <t>tshirt_style_choices</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'label':_'white'}</t>
+          <t>classic</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'label': 'White'}</t>
+          <t>Classic</t>
         </is>
       </c>
     </row>
@@ -1059,12 +1059,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'label':_'classic'}</t>
+          <t>crew</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'label': 'Classic'}</t>
+          <t>Crew</t>
         </is>
       </c>
     </row>
@@ -1076,29 +1076,29 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'label':_'crew'}</t>
+          <t>hoodie</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'label': 'Crew'}</t>
+          <t>Hoodie</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>tshirt_style_choices</t>
+          <t>tshirt_material_choices</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'label':_'hoodie'}</t>
+          <t>cotton</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'label': 'Hoodie'}</t>
+          <t>Cotton</t>
         </is>
       </c>
     </row>
@@ -1110,12 +1110,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>{'label':_'cotton'}</t>
+          <t>polyester</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>{'label': 'Cotton'}</t>
+          <t>Polyester</t>
         </is>
       </c>
     </row>
@@ -1127,29 +1127,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>{'label':_'polyester'}</t>
+          <t>blend</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>{'label': 'Polyester'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>tshirt_material_choices</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>{'label':_'blend'}</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>{'label': 'Blend'}</t>
+          <t>Blend</t>
         </is>
       </c>
     </row>
